--- a/discharge_forms/037_sports_medicine_discharge_form--discharge_forms.xlsx
+++ b/discharge_forms/037_sports_medicine_discharge_form--discharge_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'active_with_restriction'}</t>
+          <t>active_with_restriction</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Active with restriction'}</t>
+          <t>Active with restriction</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'non-active'}</t>
+          <t>non-active</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Non-Active'}</t>
+          <t>Non-Active</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'non-active_with_restriction'}</t>
+          <t>non-active_with_restriction</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Non-Active with restriction'}</t>
+          <t>Non-Active with restriction</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'unable_to_perform'}</t>
+          <t>unable_to_perform</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Unable to perform'}</t>
+          <t>Unable to perform</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'rest_and_ice'}</t>
+          <t>rest_and_ice</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Rest and Ice'}</t>
+          <t>Rest and Ice</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'stretching_and_mobilization'}</t>
+          <t>stretching_and_mobilization</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Stretching and Mobilization'}</t>
+          <t>Stretching and Mobilization</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'activity_modification'}</t>
+          <t>activity_modification</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Activity modification'}</t>
+          <t>Activity modification</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'activity_cessation'}</t>
+          <t>activity_cessation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Activity cessation'}</t>
+          <t>Activity cessation</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'not_scheduled'}</t>
+          <t>not_scheduled</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Not scheduled'}</t>
+          <t>Not scheduled</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'not_required'}</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Not required'}</t>
+          <t>Not required</t>
         </is>
       </c>
     </row>
